--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -879,39 +879,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129314039</v>
+        <v>129436156</v>
       </c>
       <c r="B4" t="n">
-        <v>5197</v>
+        <v>97262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -919,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346083</v>
+        <v>346164</v>
       </c>
       <c r="R4" t="n">
-        <v>6611330</v>
+        <v>6611359</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,38 +981,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129436156</v>
+        <v>129315274</v>
       </c>
       <c r="B5" t="n">
-        <v>97262</v>
+        <v>4870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>101675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1021,13 +1025,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346164</v>
+        <v>346052</v>
       </c>
       <c r="R5" t="n">
-        <v>6611359</v>
+        <v>6611326</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129315274</v>
+        <v>129314039</v>
       </c>
       <c r="B6" t="n">
-        <v>4870</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,32 +1099,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101675</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346052</v>
+        <v>346083</v>
       </c>
       <c r="R6" t="n">
-        <v>6611326</v>
+        <v>6611330</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1191,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129314197</v>
+        <v>129314075</v>
       </c>
       <c r="B7" t="n">
-        <v>91780</v>
+        <v>95848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1202,26 +1202,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1229,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346210</v>
+        <v>346120</v>
       </c>
       <c r="R7" t="n">
-        <v>6611444</v>
+        <v>6611435</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1292,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129314075</v>
+        <v>129314197</v>
       </c>
       <c r="B8" t="n">
-        <v>95848</v>
+        <v>91780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,27 +1304,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2362</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346120</v>
+        <v>346210</v>
       </c>
       <c r="R8" t="n">
-        <v>6611435</v>
+        <v>6611444</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129314846</v>
+        <v>129435846</v>
       </c>
       <c r="B10" t="n">
-        <v>96254</v>
+        <v>97689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>2606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346170</v>
+        <v>346116</v>
       </c>
       <c r="R10" t="n">
-        <v>6611332</v>
+        <v>6611445</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129435846</v>
+        <v>129314846</v>
       </c>
       <c r="B12" t="n">
-        <v>97689</v>
+        <v>96254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>2813</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>346116</v>
+        <v>346170</v>
       </c>
       <c r="R12" t="n">
-        <v>6611445</v>
+        <v>6611332</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314057</v>
+        <v>129435982</v>
       </c>
       <c r="B16" t="n">
         <v>97262</v>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346105</v>
+        <v>346198</v>
       </c>
       <c r="R16" t="n">
-        <v>6611430</v>
+        <v>6611512</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2211,38 +2211,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129435982</v>
+        <v>129314097</v>
       </c>
       <c r="B17" t="n">
-        <v>97262</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2250,13 +2251,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>346198</v>
+        <v>346210</v>
       </c>
       <c r="R17" t="n">
-        <v>6611512</v>
+        <v>6611507</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2313,39 +2314,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129314097</v>
+        <v>129314057</v>
       </c>
       <c r="B18" t="n">
-        <v>5197</v>
+        <v>97262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>346210</v>
+        <v>346105</v>
       </c>
       <c r="R18" t="n">
-        <v>6611507</v>
+        <v>6611430</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314180</v>
+        <v>129435818</v>
       </c>
       <c r="B23" t="n">
-        <v>97637</v>
+        <v>96242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2569</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346106</v>
+        <v>346107</v>
       </c>
       <c r="R23" t="n">
-        <v>6611460</v>
+        <v>6611387</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129435818</v>
+        <v>129314180</v>
       </c>
       <c r="B24" t="n">
-        <v>96242</v>
+        <v>97637</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>2569</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346107</v>
+        <v>346106</v>
       </c>
       <c r="R24" t="n">
-        <v>6611387</v>
+        <v>6611460</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129314244</v>
+        <v>129435288</v>
       </c>
       <c r="B26" t="n">
-        <v>5197</v>
+        <v>75355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,28 +3147,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3176,13 +3174,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346131</v>
+        <v>346193</v>
       </c>
       <c r="R26" t="n">
-        <v>6611377</v>
+        <v>6611282</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3239,10 +3237,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129435288</v>
+        <v>129314244</v>
       </c>
       <c r="B27" t="n">
-        <v>75355</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,26 +3248,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346193</v>
+        <v>346131</v>
       </c>
       <c r="R27" t="n">
-        <v>6611282</v>
+        <v>6611377</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129315527</v>
       </c>
       <c r="B2" t="n">
-        <v>97267</v>
+        <v>97273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129435802</v>
       </c>
       <c r="B3" t="n">
-        <v>95853</v>
+        <v>95859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,43 +879,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129315274</v>
+        <v>129436156</v>
       </c>
       <c r="B4" t="n">
-        <v>4870</v>
+        <v>97273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346052</v>
+        <v>346164</v>
       </c>
       <c r="R4" t="n">
-        <v>6611326</v>
+        <v>6611359</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129314039</v>
+        <v>129315274</v>
       </c>
       <c r="B5" t="n">
-        <v>5197</v>
+        <v>4870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,28 +992,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>101675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346083</v>
+        <v>346052</v>
       </c>
       <c r="R5" t="n">
-        <v>6611330</v>
+        <v>6611326</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1089,38 +1088,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129436156</v>
+        <v>129314039</v>
       </c>
       <c r="B6" t="n">
-        <v>97267</v>
+        <v>5197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346164</v>
+        <v>346083</v>
       </c>
       <c r="R6" t="n">
-        <v>6611359</v>
+        <v>6611330</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>129314197</v>
       </c>
       <c r="B7" t="n">
-        <v>91785</v>
+        <v>91791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>129314075</v>
       </c>
       <c r="B8" t="n">
-        <v>95853</v>
+        <v>95859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129314960</v>
       </c>
       <c r="B9" t="n">
-        <v>97267</v>
+        <v>97273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>129314846</v>
       </c>
       <c r="B10" t="n">
-        <v>96259</v>
+        <v>96265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129314731</v>
+        <v>129435846</v>
       </c>
       <c r="B11" t="n">
-        <v>101231</v>
+        <v>97700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         <v>346116</v>
       </c>
       <c r="R11" t="n">
-        <v>6611431</v>
+        <v>6611445</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129435846</v>
+        <v>129314731</v>
       </c>
       <c r="B12" t="n">
-        <v>97694</v>
+        <v>101237</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         <v>346116</v>
       </c>
       <c r="R12" t="n">
-        <v>6611445</v>
+        <v>6611431</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129435692</v>
       </c>
       <c r="B14" t="n">
-        <v>80319</v>
+        <v>80325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>129314057</v>
       </c>
       <c r="B16" t="n">
-        <v>97267</v>
+        <v>97273</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,38 +2211,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129435982</v>
+        <v>129314097</v>
       </c>
       <c r="B17" t="n">
-        <v>97267</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2250,13 +2251,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>346198</v>
+        <v>346210</v>
       </c>
       <c r="R17" t="n">
-        <v>6611512</v>
+        <v>6611507</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2313,39 +2314,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129314097</v>
+        <v>129435982</v>
       </c>
       <c r="B18" t="n">
-        <v>5197</v>
+        <v>97273</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>346210</v>
+        <v>346198</v>
       </c>
       <c r="R18" t="n">
-        <v>6611507</v>
+        <v>6611512</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>129314070</v>
       </c>
       <c r="B19" t="n">
-        <v>97705</v>
+        <v>97711</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129433339</v>
       </c>
       <c r="B20" t="n">
-        <v>96247</v>
+        <v>96253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>129433280</v>
       </c>
       <c r="B21" t="n">
-        <v>91785</v>
+        <v>91791</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>129433259</v>
       </c>
       <c r="B22" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,42 +2822,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314535</v>
+        <v>129314180</v>
       </c>
       <c r="B23" t="n">
-        <v>57892</v>
+        <v>97648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2865,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346219</v>
+        <v>346106</v>
       </c>
       <c r="R23" t="n">
-        <v>6611489</v>
+        <v>6611460</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2903,17 +2899,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2935,7 +2927,7 @@
         <v>129435818</v>
       </c>
       <c r="B24" t="n">
-        <v>96247</v>
+        <v>96253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,38 +3026,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129314180</v>
+        <v>129314535</v>
       </c>
       <c r="B25" t="n">
-        <v>97642</v>
+        <v>57898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3073,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>346106</v>
+        <v>346219</v>
       </c>
       <c r="R25" t="n">
-        <v>6611460</v>
+        <v>6611489</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3111,13 +3107,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129435288</v>
+        <v>129314244</v>
       </c>
       <c r="B26" t="n">
-        <v>75360</v>
+        <v>5197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,26 +3147,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3174,13 +3176,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346193</v>
+        <v>346131</v>
       </c>
       <c r="R26" t="n">
-        <v>6611282</v>
+        <v>6611377</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3237,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314244</v>
+        <v>129435288</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>75366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3248,28 +3250,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346131</v>
+        <v>346193</v>
       </c>
       <c r="R27" t="n">
-        <v>6611377</v>
+        <v>6611282</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -1191,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129314197</v>
+        <v>129314075</v>
       </c>
       <c r="B7" t="n">
-        <v>91791</v>
+        <v>95859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1202,26 +1202,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1229,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346210</v>
+        <v>346120</v>
       </c>
       <c r="R7" t="n">
-        <v>6611444</v>
+        <v>6611435</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1292,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129314075</v>
+        <v>129314197</v>
       </c>
       <c r="B8" t="n">
-        <v>95859</v>
+        <v>91791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,27 +1304,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2362</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346120</v>
+        <v>346210</v>
       </c>
       <c r="R8" t="n">
-        <v>6611435</v>
+        <v>6611444</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -2518,38 +2518,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433339</v>
+        <v>129433259</v>
       </c>
       <c r="B20" t="n">
-        <v>96253</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2557,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>346089</v>
+        <v>346217</v>
       </c>
       <c r="R20" t="n">
-        <v>6611400</v>
+        <v>6611376</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2620,10 +2619,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433280</v>
+        <v>129433339</v>
       </c>
       <c r="B21" t="n">
-        <v>91791</v>
+        <v>96253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,26 +2630,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>346163</v>
+        <v>346089</v>
       </c>
       <c r="R21" t="n">
-        <v>6611351</v>
+        <v>6611400</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433259</v>
+        <v>129433280</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>91791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>346217</v>
+        <v>346163</v>
       </c>
       <c r="R22" t="n">
-        <v>6611376</v>
+        <v>6611351</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -879,38 +879,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129436156</v>
+        <v>129314039</v>
       </c>
       <c r="B4" t="n">
-        <v>97273</v>
+        <v>5197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -918,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346164</v>
+        <v>346083</v>
       </c>
       <c r="R4" t="n">
-        <v>6611359</v>
+        <v>6611330</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1088,39 +1089,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129314039</v>
+        <v>129436156</v>
       </c>
       <c r="B6" t="n">
-        <v>5197</v>
+        <v>97273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346083</v>
+        <v>346164</v>
       </c>
       <c r="R6" t="n">
-        <v>6611330</v>
+        <v>6611359</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129314846</v>
+        <v>129435846</v>
       </c>
       <c r="B10" t="n">
-        <v>96265</v>
+        <v>97700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>2606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346170</v>
+        <v>346116</v>
       </c>
       <c r="R10" t="n">
-        <v>6611332</v>
+        <v>6611445</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129435846</v>
+        <v>129314846</v>
       </c>
       <c r="B11" t="n">
-        <v>97700</v>
+        <v>96265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>2813</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>346116</v>
+        <v>346170</v>
       </c>
       <c r="R11" t="n">
-        <v>6611445</v>
+        <v>6611332</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314057</v>
+        <v>129435982</v>
       </c>
       <c r="B16" t="n">
         <v>97273</v>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346105</v>
+        <v>346198</v>
       </c>
       <c r="R16" t="n">
-        <v>6611430</v>
+        <v>6611512</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129435982</v>
+        <v>129314057</v>
       </c>
       <c r="B18" t="n">
         <v>97273</v>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>346198</v>
+        <v>346105</v>
       </c>
       <c r="R18" t="n">
-        <v>6611512</v>
+        <v>6611430</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2518,37 +2518,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433259</v>
+        <v>129433339</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>96253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2556,10 +2557,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>346217</v>
+        <v>346089</v>
       </c>
       <c r="R20" t="n">
-        <v>6611376</v>
+        <v>6611400</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2619,38 +2620,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433339</v>
+        <v>129433259</v>
       </c>
       <c r="B21" t="n">
-        <v>96253</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>346089</v>
+        <v>346217</v>
       </c>
       <c r="R21" t="n">
-        <v>6611400</v>
+        <v>6611376</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2822,38 +2822,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314180</v>
+        <v>129314535</v>
       </c>
       <c r="B23" t="n">
-        <v>97648</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2861,10 +2865,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346106</v>
+        <v>346219</v>
       </c>
       <c r="R23" t="n">
-        <v>6611460</v>
+        <v>6611489</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2899,13 +2903,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3026,42 +3034,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129314535</v>
+        <v>129314180</v>
       </c>
       <c r="B25" t="n">
-        <v>57898</v>
+        <v>97648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3069,10 +3073,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>346219</v>
+        <v>346106</v>
       </c>
       <c r="R25" t="n">
-        <v>6611489</v>
+        <v>6611460</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3107,17 +3111,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129314244</v>
+        <v>129435288</v>
       </c>
       <c r="B26" t="n">
-        <v>5197</v>
+        <v>75366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,28 +3147,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3176,13 +3174,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346131</v>
+        <v>346193</v>
       </c>
       <c r="R26" t="n">
-        <v>6611377</v>
+        <v>6611282</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3239,10 +3237,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129435288</v>
+        <v>129314244</v>
       </c>
       <c r="B27" t="n">
-        <v>75366</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,26 +3248,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346193</v>
+        <v>346131</v>
       </c>
       <c r="R27" t="n">
-        <v>6611282</v>
+        <v>6611377</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -2109,7 +2109,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129435982</v>
+        <v>129314057</v>
       </c>
       <c r="B16" t="n">
         <v>97273</v>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346198</v>
+        <v>346105</v>
       </c>
       <c r="R16" t="n">
-        <v>6611512</v>
+        <v>6611430</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129314057</v>
+        <v>129435982</v>
       </c>
       <c r="B18" t="n">
         <v>97273</v>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>346105</v>
+        <v>346198</v>
       </c>
       <c r="R18" t="n">
-        <v>6611430</v>
+        <v>6611512</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129435288</v>
+        <v>129314244</v>
       </c>
       <c r="B26" t="n">
-        <v>75366</v>
+        <v>5197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,26 +3147,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3174,13 +3176,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346193</v>
+        <v>346131</v>
       </c>
       <c r="R26" t="n">
-        <v>6611282</v>
+        <v>6611377</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3237,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314244</v>
+        <v>129435288</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>75366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3248,28 +3250,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346131</v>
+        <v>346193</v>
       </c>
       <c r="R27" t="n">
-        <v>6611377</v>
+        <v>6611282</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129315527</v>
       </c>
       <c r="B2" t="n">
-        <v>97273</v>
+        <v>97274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129435802</v>
       </c>
       <c r="B3" t="n">
-        <v>95859</v>
+        <v>95860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129314039</v>
+        <v>129315274</v>
       </c>
       <c r="B4" t="n">
-        <v>5197</v>
+        <v>4870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,28 +890,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>101675</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346083</v>
+        <v>346052</v>
       </c>
       <c r="R4" t="n">
-        <v>6611330</v>
+        <v>6611326</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -982,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129315274</v>
+        <v>129314039</v>
       </c>
       <c r="B5" t="n">
-        <v>4870</v>
+        <v>5197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,32 +997,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101675</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346052</v>
+        <v>346083</v>
       </c>
       <c r="R5" t="n">
-        <v>6611326</v>
+        <v>6611330</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1092,7 +1092,7 @@
         <v>129436156</v>
       </c>
       <c r="B6" t="n">
-        <v>97273</v>
+        <v>97274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>129314075</v>
       </c>
       <c r="B7" t="n">
-        <v>95859</v>
+        <v>95860</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129314960</v>
       </c>
       <c r="B9" t="n">
-        <v>97273</v>
+        <v>97274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129435846</v>
+        <v>129314846</v>
       </c>
       <c r="B10" t="n">
-        <v>97700</v>
+        <v>96266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2606</v>
+        <v>2813</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346116</v>
+        <v>346170</v>
       </c>
       <c r="R10" t="n">
-        <v>6611445</v>
+        <v>6611332</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129314846</v>
+        <v>129314731</v>
       </c>
       <c r="B11" t="n">
-        <v>96265</v>
+        <v>101238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>346170</v>
+        <v>346116</v>
       </c>
       <c r="R11" t="n">
-        <v>6611332</v>
+        <v>6611431</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129314731</v>
+        <v>129435846</v>
       </c>
       <c r="B12" t="n">
-        <v>101237</v>
+        <v>97701</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         <v>346116</v>
       </c>
       <c r="R12" t="n">
-        <v>6611431</v>
+        <v>6611445</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314057</v>
+        <v>129435982</v>
       </c>
       <c r="B16" t="n">
-        <v>97273</v>
+        <v>97274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346105</v>
+        <v>346198</v>
       </c>
       <c r="R16" t="n">
-        <v>6611430</v>
+        <v>6611512</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2211,39 +2211,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129314097</v>
+        <v>129314057</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>97274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2251,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>346210</v>
+        <v>346105</v>
       </c>
       <c r="R17" t="n">
-        <v>6611507</v>
+        <v>6611430</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2314,38 +2313,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129435982</v>
+        <v>129314097</v>
       </c>
       <c r="B18" t="n">
-        <v>97273</v>
+        <v>5197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>346198</v>
+        <v>346210</v>
       </c>
       <c r="R18" t="n">
-        <v>6611512</v>
+        <v>6611507</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>129314070</v>
       </c>
       <c r="B19" t="n">
-        <v>97711</v>
+        <v>97712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129433339</v>
       </c>
       <c r="B20" t="n">
-        <v>96253</v>
+        <v>96254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433259</v>
+        <v>129433280</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>91791</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>346217</v>
+        <v>346163</v>
       </c>
       <c r="R21" t="n">
-        <v>6611376</v>
+        <v>6611351</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433280</v>
+        <v>129433259</v>
       </c>
       <c r="B22" t="n">
-        <v>91791</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>346163</v>
+        <v>346217</v>
       </c>
       <c r="R22" t="n">
-        <v>6611351</v>
+        <v>6611376</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2822,42 +2822,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314535</v>
+        <v>129314180</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>97649</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2865,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346219</v>
+        <v>346106</v>
       </c>
       <c r="R23" t="n">
-        <v>6611489</v>
+        <v>6611460</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2903,17 +2899,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2932,38 +2924,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129435818</v>
+        <v>129314535</v>
       </c>
       <c r="B24" t="n">
-        <v>96253</v>
+        <v>57898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2971,13 +2967,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346107</v>
+        <v>346219</v>
       </c>
       <c r="R24" t="n">
-        <v>6611387</v>
+        <v>6611489</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3009,13 +3005,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129314180</v>
+        <v>129435818</v>
       </c>
       <c r="B25" t="n">
-        <v>97648</v>
+        <v>96254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2569</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3073,13 +3073,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>346106</v>
+        <v>346107</v>
       </c>
       <c r="R25" t="n">
-        <v>6611460</v>
+        <v>6611387</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129314244</v>
+        <v>129435288</v>
       </c>
       <c r="B26" t="n">
-        <v>5197</v>
+        <v>75366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,28 +3147,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3176,13 +3174,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346131</v>
+        <v>346193</v>
       </c>
       <c r="R26" t="n">
-        <v>6611377</v>
+        <v>6611282</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3239,10 +3237,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129435288</v>
+        <v>129314244</v>
       </c>
       <c r="B27" t="n">
-        <v>75366</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,26 +3248,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346193</v>
+        <v>346131</v>
       </c>
       <c r="R27" t="n">
-        <v>6611282</v>
+        <v>6611377</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129315527</v>
+        <v>129435802</v>
       </c>
       <c r="B2" t="n">
-        <v>97274</v>
+        <v>95861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>2362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346139</v>
+        <v>346165</v>
       </c>
       <c r="R2" t="n">
-        <v>6611366</v>
+        <v>6611336</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129435802</v>
+        <v>129315527</v>
       </c>
       <c r="B3" t="n">
-        <v>95860</v>
+        <v>97275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2362</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346165</v>
+        <v>346139</v>
       </c>
       <c r="R3" t="n">
-        <v>6611336</v>
+        <v>6611366</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129315274</v>
+        <v>129314039</v>
       </c>
       <c r="B4" t="n">
-        <v>4870</v>
+        <v>5198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,32 +890,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346052</v>
+        <v>346083</v>
       </c>
       <c r="R4" t="n">
-        <v>6611326</v>
+        <v>6611330</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129314039</v>
+        <v>129315274</v>
       </c>
       <c r="B5" t="n">
-        <v>5197</v>
+        <v>4871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,28 +993,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>101675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346083</v>
+        <v>346052</v>
       </c>
       <c r="R5" t="n">
-        <v>6611330</v>
+        <v>6611326</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1092,7 +1092,7 @@
         <v>129436156</v>
       </c>
       <c r="B6" t="n">
-        <v>97274</v>
+        <v>97275</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>129314075</v>
       </c>
       <c r="B7" t="n">
-        <v>95860</v>
+        <v>95861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>129314197</v>
       </c>
       <c r="B8" t="n">
-        <v>91791</v>
+        <v>91792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129314960</v>
       </c>
       <c r="B9" t="n">
-        <v>97274</v>
+        <v>97275</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129314846</v>
+        <v>129314731</v>
       </c>
       <c r="B10" t="n">
-        <v>96266</v>
+        <v>101239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346170</v>
+        <v>346116</v>
       </c>
       <c r="R10" t="n">
-        <v>6611332</v>
+        <v>6611431</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129314731</v>
+        <v>129314846</v>
       </c>
       <c r="B11" t="n">
-        <v>101238</v>
+        <v>96267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>346116</v>
+        <v>346170</v>
       </c>
       <c r="R11" t="n">
-        <v>6611431</v>
+        <v>6611332</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1703,7 +1703,7 @@
         <v>129435846</v>
       </c>
       <c r="B12" t="n">
-        <v>97701</v>
+        <v>97702</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>129314127</v>
       </c>
       <c r="B13" t="n">
-        <v>4773</v>
+        <v>4774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129435692</v>
       </c>
       <c r="B14" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>129315075</v>
       </c>
       <c r="B15" t="n">
-        <v>5197</v>
+        <v>5198</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129435982</v>
+        <v>129314057</v>
       </c>
       <c r="B16" t="n">
-        <v>97274</v>
+        <v>97275</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346198</v>
+        <v>346105</v>
       </c>
       <c r="R16" t="n">
-        <v>6611512</v>
+        <v>6611430</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2211,38 +2211,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129314057</v>
+        <v>129314097</v>
       </c>
       <c r="B17" t="n">
-        <v>97274</v>
+        <v>5198</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2250,10 +2251,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>346105</v>
+        <v>346210</v>
       </c>
       <c r="R17" t="n">
-        <v>6611430</v>
+        <v>6611507</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2313,39 +2314,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129314097</v>
+        <v>129435982</v>
       </c>
       <c r="B18" t="n">
-        <v>5197</v>
+        <v>97275</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>346210</v>
+        <v>346198</v>
       </c>
       <c r="R18" t="n">
-        <v>6611507</v>
+        <v>6611512</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>129314070</v>
       </c>
       <c r="B19" t="n">
-        <v>97712</v>
+        <v>97713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433339</v>
+        <v>129433280</v>
       </c>
       <c r="B20" t="n">
-        <v>96254</v>
+        <v>91792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,27 +2529,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2557,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>346089</v>
+        <v>346163</v>
       </c>
       <c r="R20" t="n">
-        <v>6611400</v>
+        <v>6611351</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2620,32 +2619,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433280</v>
+        <v>129433259</v>
       </c>
       <c r="B21" t="n">
-        <v>91791</v>
+        <v>79261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>346163</v>
+        <v>346217</v>
       </c>
       <c r="R21" t="n">
-        <v>6611351</v>
+        <v>6611376</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2721,37 +2720,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433259</v>
+        <v>129433339</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>96255</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>346217</v>
+        <v>346089</v>
       </c>
       <c r="R22" t="n">
-        <v>6611376</v>
+        <v>6611400</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2822,38 +2822,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314180</v>
+        <v>129314535</v>
       </c>
       <c r="B23" t="n">
-        <v>97649</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2861,10 +2865,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346106</v>
+        <v>346219</v>
       </c>
       <c r="R23" t="n">
-        <v>6611460</v>
+        <v>6611489</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2899,13 +2903,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2924,42 +2932,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129314535</v>
+        <v>129314180</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>97650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2967,10 +2971,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346219</v>
+        <v>346106</v>
       </c>
       <c r="R24" t="n">
-        <v>6611489</v>
+        <v>6611460</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3005,17 +3009,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>129435818</v>
       </c>
       <c r="B25" t="n">
-        <v>96254</v>
+        <v>96255</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129435288</v>
       </c>
       <c r="B26" t="n">
-        <v>75366</v>
+        <v>75367</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>129314244</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>5198</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129435802</v>
       </c>
       <c r="B2" t="n">
-        <v>95861</v>
+        <v>95864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129315527</v>
       </c>
       <c r="B3" t="n">
-        <v>97275</v>
+        <v>97278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129314039</v>
+        <v>129315274</v>
       </c>
       <c r="B4" t="n">
-        <v>5198</v>
+        <v>4871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,28 +890,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>101675</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346083</v>
+        <v>346052</v>
       </c>
       <c r="R4" t="n">
-        <v>6611330</v>
+        <v>6611326</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -982,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129315274</v>
+        <v>129314039</v>
       </c>
       <c r="B5" t="n">
-        <v>4871</v>
+        <v>5198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,32 +997,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101675</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346052</v>
+        <v>346083</v>
       </c>
       <c r="R5" t="n">
-        <v>6611326</v>
+        <v>6611330</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1092,7 +1092,7 @@
         <v>129436156</v>
       </c>
       <c r="B6" t="n">
-        <v>97275</v>
+        <v>97278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>129314075</v>
       </c>
       <c r="B7" t="n">
-        <v>95861</v>
+        <v>95864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>129314197</v>
       </c>
       <c r="B8" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129314960</v>
       </c>
       <c r="B9" t="n">
-        <v>97275</v>
+        <v>97278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129314731</v>
+        <v>129314846</v>
       </c>
       <c r="B10" t="n">
-        <v>101239</v>
+        <v>96270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2813</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346116</v>
+        <v>346170</v>
       </c>
       <c r="R10" t="n">
-        <v>6611431</v>
+        <v>6611332</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129314846</v>
+        <v>129314731</v>
       </c>
       <c r="B11" t="n">
-        <v>96267</v>
+        <v>101242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>346170</v>
+        <v>346116</v>
       </c>
       <c r="R11" t="n">
-        <v>6611332</v>
+        <v>6611431</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1703,7 +1703,7 @@
         <v>129435846</v>
       </c>
       <c r="B12" t="n">
-        <v>97702</v>
+        <v>97705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129435692</v>
       </c>
       <c r="B14" t="n">
-        <v>80326</v>
+        <v>80329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>129314057</v>
       </c>
       <c r="B16" t="n">
-        <v>97275</v>
+        <v>97278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129435982</v>
       </c>
       <c r="B18" t="n">
-        <v>97275</v>
+        <v>97278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>129314070</v>
       </c>
       <c r="B19" t="n">
-        <v>97713</v>
+        <v>97716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129433280</v>
       </c>
       <c r="B20" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>129433259</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>129433339</v>
       </c>
       <c r="B22" t="n">
-        <v>96255</v>
+        <v>96258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>129314535</v>
       </c>
       <c r="B23" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,10 +2932,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129314180</v>
+        <v>129435818</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
+        <v>96258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2943,21 +2943,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2569</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346106</v>
+        <v>346107</v>
       </c>
       <c r="R24" t="n">
-        <v>6611460</v>
+        <v>6611387</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129435818</v>
+        <v>129314180</v>
       </c>
       <c r="B25" t="n">
-        <v>96255</v>
+        <v>97653</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>2569</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3073,13 +3073,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>346107</v>
+        <v>346106</v>
       </c>
       <c r="R25" t="n">
-        <v>6611387</v>
+        <v>6611460</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129435288</v>
+        <v>129314244</v>
       </c>
       <c r="B26" t="n">
-        <v>75367</v>
+        <v>5198</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,26 +3147,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3174,13 +3176,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346193</v>
+        <v>346131</v>
       </c>
       <c r="R26" t="n">
-        <v>6611282</v>
+        <v>6611377</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3237,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314244</v>
+        <v>129435288</v>
       </c>
       <c r="B27" t="n">
-        <v>5198</v>
+        <v>75370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3248,28 +3250,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346131</v>
+        <v>346193</v>
       </c>
       <c r="R27" t="n">
-        <v>6611377</v>
+        <v>6611282</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129435802</v>
+        <v>129315527</v>
       </c>
       <c r="B2" t="n">
-        <v>95864</v>
+        <v>97278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2362</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346165</v>
+        <v>346139</v>
       </c>
       <c r="R2" t="n">
-        <v>6611336</v>
+        <v>6611366</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129315527</v>
+        <v>129435802</v>
       </c>
       <c r="B3" t="n">
-        <v>97278</v>
+        <v>95864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>2362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346139</v>
+        <v>346165</v>
       </c>
       <c r="R3" t="n">
-        <v>6611366</v>
+        <v>6611336</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129315274</v>
+        <v>129314039</v>
       </c>
       <c r="B4" t="n">
-        <v>4871</v>
+        <v>5198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,32 +890,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346052</v>
+        <v>346083</v>
       </c>
       <c r="R4" t="n">
-        <v>6611326</v>
+        <v>6611330</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,39 +982,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129314039</v>
+        <v>129436156</v>
       </c>
       <c r="B5" t="n">
-        <v>5198</v>
+        <v>97278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346083</v>
+        <v>346164</v>
       </c>
       <c r="R5" t="n">
-        <v>6611330</v>
+        <v>6611359</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,38 +1084,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129436156</v>
+        <v>129315274</v>
       </c>
       <c r="B6" t="n">
-        <v>97278</v>
+        <v>4871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>101675</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346164</v>
+        <v>346052</v>
       </c>
       <c r="R6" t="n">
-        <v>6611359</v>
+        <v>6611326</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129314846</v>
+        <v>129314731</v>
       </c>
       <c r="B10" t="n">
-        <v>96270</v>
+        <v>101243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346170</v>
+        <v>346116</v>
       </c>
       <c r="R10" t="n">
-        <v>6611332</v>
+        <v>6611431</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129314731</v>
+        <v>129435846</v>
       </c>
       <c r="B11" t="n">
-        <v>101242</v>
+        <v>97705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         <v>346116</v>
       </c>
       <c r="R11" t="n">
-        <v>6611431</v>
+        <v>6611445</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129435846</v>
+        <v>129314846</v>
       </c>
       <c r="B12" t="n">
-        <v>97705</v>
+        <v>96270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>2813</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>346116</v>
+        <v>346170</v>
       </c>
       <c r="R12" t="n">
-        <v>6611445</v>
+        <v>6611332</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2109,38 +2109,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314057</v>
+        <v>129314097</v>
       </c>
       <c r="B16" t="n">
-        <v>97278</v>
+        <v>5198</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2148,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346105</v>
+        <v>346210</v>
       </c>
       <c r="R16" t="n">
-        <v>6611430</v>
+        <v>6611507</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2211,39 +2212,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129314097</v>
+        <v>129314057</v>
       </c>
       <c r="B17" t="n">
-        <v>5198</v>
+        <v>97278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>346210</v>
+        <v>346105</v>
       </c>
       <c r="R17" t="n">
-        <v>6611507</v>
+        <v>6611430</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433280</v>
+        <v>129433339</v>
       </c>
       <c r="B20" t="n">
-        <v>91795</v>
+        <v>96258</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,26 +2529,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2556,10 +2557,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>346163</v>
+        <v>346089</v>
       </c>
       <c r="R20" t="n">
-        <v>6611351</v>
+        <v>6611400</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2619,32 +2620,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433259</v>
+        <v>129433280</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>346217</v>
+        <v>346163</v>
       </c>
       <c r="R21" t="n">
-        <v>6611376</v>
+        <v>6611351</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2720,38 +2721,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433339</v>
+        <v>129433259</v>
       </c>
       <c r="B22" t="n">
-        <v>96258</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>346089</v>
+        <v>346217</v>
       </c>
       <c r="R22" t="n">
-        <v>6611400</v>
+        <v>6611376</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2822,42 +2822,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314535</v>
+        <v>129435818</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>96258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2865,13 +2861,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346219</v>
+        <v>346107</v>
       </c>
       <c r="R23" t="n">
-        <v>6611489</v>
+        <v>6611387</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2903,17 +2899,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2932,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129435818</v>
+        <v>129314180</v>
       </c>
       <c r="B24" t="n">
-        <v>96258</v>
+        <v>97653</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2943,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>2569</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2971,13 +2963,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346107</v>
+        <v>346106</v>
       </c>
       <c r="R24" t="n">
-        <v>6611387</v>
+        <v>6611460</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3034,38 +3026,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129314180</v>
+        <v>129314535</v>
       </c>
       <c r="B25" t="n">
-        <v>97653</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3073,10 +3069,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>346106</v>
+        <v>346219</v>
       </c>
       <c r="R25" t="n">
-        <v>6611460</v>
+        <v>6611489</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3111,13 +3107,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129314244</v>
+        <v>129435288</v>
       </c>
       <c r="B26" t="n">
-        <v>5198</v>
+        <v>75370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,28 +3147,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3176,13 +3174,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346131</v>
+        <v>346193</v>
       </c>
       <c r="R26" t="n">
-        <v>6611377</v>
+        <v>6611282</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3239,10 +3237,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129435288</v>
+        <v>129314244</v>
       </c>
       <c r="B27" t="n">
-        <v>75370</v>
+        <v>5198</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,26 +3248,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346193</v>
+        <v>346131</v>
       </c>
       <c r="R27" t="n">
-        <v>6611282</v>
+        <v>6611377</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129314039</v>
+        <v>129315274</v>
       </c>
       <c r="B4" t="n">
-        <v>5198</v>
+        <v>4871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,28 +890,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>101675</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346083</v>
+        <v>346052</v>
       </c>
       <c r="R4" t="n">
-        <v>6611330</v>
+        <v>6611326</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -982,38 +986,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129436156</v>
+        <v>129314039</v>
       </c>
       <c r="B5" t="n">
-        <v>97278</v>
+        <v>5198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1021,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346164</v>
+        <v>346083</v>
       </c>
       <c r="R5" t="n">
-        <v>6611359</v>
+        <v>6611330</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,43 +1089,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129315274</v>
+        <v>129436156</v>
       </c>
       <c r="B6" t="n">
-        <v>4871</v>
+        <v>97278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101675</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346052</v>
+        <v>346164</v>
       </c>
       <c r="R6" t="n">
-        <v>6611326</v>
+        <v>6611359</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129314075</v>
+        <v>129314197</v>
       </c>
       <c r="B7" t="n">
-        <v>95864</v>
+        <v>91795</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1202,27 +1202,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2362</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1230,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346120</v>
+        <v>346210</v>
       </c>
       <c r="R7" t="n">
-        <v>6611435</v>
+        <v>6611444</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1293,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129314197</v>
+        <v>129314075</v>
       </c>
       <c r="B8" t="n">
-        <v>91795</v>
+        <v>95864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1304,26 +1303,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>2362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346210</v>
+        <v>346120</v>
       </c>
       <c r="R8" t="n">
-        <v>6611444</v>
+        <v>6611435</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129314731</v>
+        <v>129435846</v>
       </c>
       <c r="B10" t="n">
-        <v>101243</v>
+        <v>97705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         <v>346116</v>
       </c>
       <c r="R10" t="n">
-        <v>6611431</v>
+        <v>6611445</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129435846</v>
+        <v>129314846</v>
       </c>
       <c r="B11" t="n">
-        <v>97705</v>
+        <v>96270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>2813</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>346116</v>
+        <v>346170</v>
       </c>
       <c r="R11" t="n">
-        <v>6611445</v>
+        <v>6611332</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129314846</v>
+        <v>129314731</v>
       </c>
       <c r="B12" t="n">
-        <v>96270</v>
+        <v>101243</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>346170</v>
+        <v>346116</v>
       </c>
       <c r="R12" t="n">
-        <v>6611332</v>
+        <v>6611431</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129435818</v>
+        <v>129314180</v>
       </c>
       <c r="B23" t="n">
-        <v>96258</v>
+        <v>97653</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>2569</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2861,13 +2861,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346107</v>
+        <v>346106</v>
       </c>
       <c r="R23" t="n">
-        <v>6611387</v>
+        <v>6611460</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,38 +2924,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129314180</v>
+        <v>129314535</v>
       </c>
       <c r="B24" t="n">
-        <v>97653</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2963,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346106</v>
+        <v>346219</v>
       </c>
       <c r="R24" t="n">
-        <v>6611460</v>
+        <v>6611489</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3001,13 +3005,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3026,42 +3034,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129314535</v>
+        <v>129435818</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>96258</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3069,13 +3073,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>346219</v>
+        <v>346107</v>
       </c>
       <c r="R25" t="n">
-        <v>6611489</v>
+        <v>6611387</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3107,17 +3111,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129435288</v>
+        <v>129314244</v>
       </c>
       <c r="B26" t="n">
-        <v>75370</v>
+        <v>5198</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,26 +3147,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3174,13 +3176,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346193</v>
+        <v>346131</v>
       </c>
       <c r="R26" t="n">
-        <v>6611282</v>
+        <v>6611377</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3237,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314244</v>
+        <v>129435288</v>
       </c>
       <c r="B27" t="n">
-        <v>5198</v>
+        <v>75370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3248,28 +3250,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346131</v>
+        <v>346193</v>
       </c>
       <c r="R27" t="n">
-        <v>6611377</v>
+        <v>6611282</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129435846</v>
+        <v>129314846</v>
       </c>
       <c r="B10" t="n">
-        <v>97705</v>
+        <v>96270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2606</v>
+        <v>2813</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346116</v>
+        <v>346170</v>
       </c>
       <c r="R10" t="n">
-        <v>6611445</v>
+        <v>6611332</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129314846</v>
+        <v>129314731</v>
       </c>
       <c r="B11" t="n">
-        <v>96270</v>
+        <v>101243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2813</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>346170</v>
+        <v>346116</v>
       </c>
       <c r="R11" t="n">
-        <v>6611332</v>
+        <v>6611431</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129314731</v>
+        <v>129435846</v>
       </c>
       <c r="B12" t="n">
-        <v>101243</v>
+        <v>97705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         <v>346116</v>
       </c>
       <c r="R12" t="n">
-        <v>6611431</v>
+        <v>6611445</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2109,39 +2109,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314097</v>
+        <v>129314057</v>
       </c>
       <c r="B16" t="n">
-        <v>5198</v>
+        <v>97278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2149,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346210</v>
+        <v>346105</v>
       </c>
       <c r="R16" t="n">
-        <v>6611507</v>
+        <v>6611430</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2212,38 +2211,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129314057</v>
+        <v>129314097</v>
       </c>
       <c r="B17" t="n">
-        <v>97278</v>
+        <v>5198</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>346105</v>
+        <v>346210</v>
       </c>
       <c r="R17" t="n">
-        <v>6611430</v>
+        <v>6611507</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433280</v>
+        <v>129433259</v>
       </c>
       <c r="B21" t="n">
-        <v>91795</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>346163</v>
+        <v>346217</v>
       </c>
       <c r="R21" t="n">
-        <v>6611351</v>
+        <v>6611376</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433259</v>
+        <v>129433280</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>346217</v>
+        <v>346163</v>
       </c>
       <c r="R22" t="n">
-        <v>6611376</v>
+        <v>6611351</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129315527</v>
       </c>
       <c r="B2" t="n">
-        <v>97278</v>
+        <v>97284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129435802</v>
       </c>
       <c r="B3" t="n">
-        <v>95864</v>
+        <v>95870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129315274</v>
+        <v>129314039</v>
       </c>
       <c r="B4" t="n">
-        <v>4871</v>
+        <v>5198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,32 +890,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346052</v>
+        <v>346083</v>
       </c>
       <c r="R4" t="n">
-        <v>6611326</v>
+        <v>6611330</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129314039</v>
+        <v>129315274</v>
       </c>
       <c r="B5" t="n">
-        <v>5198</v>
+        <v>4871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,28 +993,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>101675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346083</v>
+        <v>346052</v>
       </c>
       <c r="R5" t="n">
-        <v>6611330</v>
+        <v>6611326</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1092,7 +1092,7 @@
         <v>129436156</v>
       </c>
       <c r="B6" t="n">
-        <v>97278</v>
+        <v>97284</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>129314197</v>
       </c>
       <c r="B7" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>129314075</v>
       </c>
       <c r="B8" t="n">
-        <v>95864</v>
+        <v>95870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129314960</v>
       </c>
       <c r="B9" t="n">
-        <v>97278</v>
+        <v>97284</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>129314846</v>
       </c>
       <c r="B10" t="n">
-        <v>96270</v>
+        <v>96276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129314731</v>
+        <v>129435846</v>
       </c>
       <c r="B11" t="n">
-        <v>101243</v>
+        <v>97711</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         <v>346116</v>
       </c>
       <c r="R11" t="n">
-        <v>6611431</v>
+        <v>6611445</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129435846</v>
+        <v>129314731</v>
       </c>
       <c r="B12" t="n">
-        <v>97705</v>
+        <v>101249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         <v>346116</v>
       </c>
       <c r="R12" t="n">
-        <v>6611445</v>
+        <v>6611431</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129435692</v>
       </c>
       <c r="B14" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>129314057</v>
       </c>
       <c r="B16" t="n">
-        <v>97278</v>
+        <v>97284</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129435982</v>
       </c>
       <c r="B18" t="n">
-        <v>97278</v>
+        <v>97284</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>129314070</v>
       </c>
       <c r="B19" t="n">
-        <v>97716</v>
+        <v>97722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129433339</v>
       </c>
       <c r="B20" t="n">
-        <v>96258</v>
+        <v>96264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>129433259</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>129433280</v>
       </c>
       <c r="B22" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,38 +2822,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314180</v>
+        <v>129314535</v>
       </c>
       <c r="B23" t="n">
-        <v>97653</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2861,10 +2865,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346106</v>
+        <v>346219</v>
       </c>
       <c r="R23" t="n">
-        <v>6611460</v>
+        <v>6611489</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2899,13 +2903,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2924,42 +2932,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129314535</v>
+        <v>129314180</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>97659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2967,10 +2971,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346219</v>
+        <v>346106</v>
       </c>
       <c r="R24" t="n">
-        <v>6611489</v>
+        <v>6611460</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3005,17 +3009,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>129435818</v>
       </c>
       <c r="B25" t="n">
-        <v>96258</v>
+        <v>96264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129314244</v>
+        <v>129435288</v>
       </c>
       <c r="B26" t="n">
-        <v>5198</v>
+        <v>75372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,28 +3147,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3176,13 +3174,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346131</v>
+        <v>346193</v>
       </c>
       <c r="R26" t="n">
-        <v>6611377</v>
+        <v>6611282</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3239,10 +3237,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129435288</v>
+        <v>129314244</v>
       </c>
       <c r="B27" t="n">
-        <v>75370</v>
+        <v>5198</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,26 +3248,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346193</v>
+        <v>346131</v>
       </c>
       <c r="R27" t="n">
-        <v>6611282</v>
+        <v>6611377</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129314039</v>
+        <v>129315274</v>
       </c>
       <c r="B4" t="n">
-        <v>5198</v>
+        <v>4871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,28 +890,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>101675</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346083</v>
+        <v>346052</v>
       </c>
       <c r="R4" t="n">
-        <v>6611330</v>
+        <v>6611326</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -982,43 +986,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129315274</v>
+        <v>129436156</v>
       </c>
       <c r="B5" t="n">
-        <v>4871</v>
+        <v>97284</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101675</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,13 +1025,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346052</v>
+        <v>346164</v>
       </c>
       <c r="R5" t="n">
-        <v>6611326</v>
+        <v>6611359</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,38 +1088,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129436156</v>
+        <v>129314039</v>
       </c>
       <c r="B6" t="n">
-        <v>97284</v>
+        <v>5198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346164</v>
+        <v>346083</v>
       </c>
       <c r="R6" t="n">
-        <v>6611359</v>
+        <v>6611330</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433259</v>
+        <v>129433280</v>
       </c>
       <c r="B21" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>346217</v>
+        <v>346163</v>
       </c>
       <c r="R21" t="n">
-        <v>6611376</v>
+        <v>6611351</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2721,32 +2721,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433280</v>
+        <v>129433259</v>
       </c>
       <c r="B22" t="n">
-        <v>91801</v>
+        <v>79266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>346163</v>
+        <v>346217</v>
       </c>
       <c r="R22" t="n">
-        <v>6611351</v>
+        <v>6611376</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129315274</v>
+        <v>129314039</v>
       </c>
       <c r="B4" t="n">
-        <v>4871</v>
+        <v>5198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,32 +890,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346052</v>
+        <v>346083</v>
       </c>
       <c r="R4" t="n">
-        <v>6611326</v>
+        <v>6611330</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,38 +982,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129436156</v>
+        <v>129315274</v>
       </c>
       <c r="B5" t="n">
-        <v>97284</v>
+        <v>4871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>101675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1025,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346164</v>
+        <v>346052</v>
       </c>
       <c r="R5" t="n">
-        <v>6611359</v>
+        <v>6611326</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,39 +1089,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129314039</v>
+        <v>129436156</v>
       </c>
       <c r="B6" t="n">
-        <v>5198</v>
+        <v>97284</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346083</v>
+        <v>346164</v>
       </c>
       <c r="R6" t="n">
-        <v>6611330</v>
+        <v>6611359</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2822,42 +2822,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314535</v>
+        <v>129314180</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>97659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2865,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346219</v>
+        <v>346106</v>
       </c>
       <c r="R23" t="n">
-        <v>6611489</v>
+        <v>6611460</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2903,17 +2899,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2932,38 +2924,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129314180</v>
+        <v>129314535</v>
       </c>
       <c r="B24" t="n">
-        <v>97659</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2971,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346106</v>
+        <v>346219</v>
       </c>
       <c r="R24" t="n">
-        <v>6611460</v>
+        <v>6611489</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3009,13 +3005,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -2822,38 +2822,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314180</v>
+        <v>129314535</v>
       </c>
       <c r="B23" t="n">
-        <v>97659</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2861,10 +2865,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346106</v>
+        <v>346219</v>
       </c>
       <c r="R23" t="n">
-        <v>6611460</v>
+        <v>6611489</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2899,13 +2903,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2924,42 +2932,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129314535</v>
+        <v>129314180</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>97659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2967,10 +2971,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346219</v>
+        <v>346106</v>
       </c>
       <c r="R24" t="n">
-        <v>6611489</v>
+        <v>6611460</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3005,17 +3009,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129435846</v>
+        <v>129314731</v>
       </c>
       <c r="B11" t="n">
-        <v>97711</v>
+        <v>101249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         <v>346116</v>
       </c>
       <c r="R11" t="n">
-        <v>6611445</v>
+        <v>6611431</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129314731</v>
+        <v>129435846</v>
       </c>
       <c r="B12" t="n">
-        <v>101249</v>
+        <v>97711</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         <v>346116</v>
       </c>
       <c r="R12" t="n">
-        <v>6611431</v>
+        <v>6611445</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129314731</v>
+        <v>129435846</v>
       </c>
       <c r="B11" t="n">
-        <v>101249</v>
+        <v>97711</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         <v>346116</v>
       </c>
       <c r="R11" t="n">
-        <v>6611431</v>
+        <v>6611445</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129435846</v>
+        <v>129314731</v>
       </c>
       <c r="B12" t="n">
-        <v>97711</v>
+        <v>101249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         <v>346116</v>
       </c>
       <c r="R12" t="n">
-        <v>6611445</v>
+        <v>6611431</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129435288</v>
+        <v>129314244</v>
       </c>
       <c r="B26" t="n">
-        <v>75372</v>
+        <v>5198</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,26 +3147,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3174,13 +3176,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346193</v>
+        <v>346131</v>
       </c>
       <c r="R26" t="n">
-        <v>6611282</v>
+        <v>6611377</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3237,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129314244</v>
+        <v>129435288</v>
       </c>
       <c r="B27" t="n">
-        <v>5198</v>
+        <v>75372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3248,28 +3250,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346131</v>
+        <v>346193</v>
       </c>
       <c r="R27" t="n">
-        <v>6611377</v>
+        <v>6611282</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129315527</v>
+        <v>129435802</v>
       </c>
       <c r="B2" t="n">
-        <v>97284</v>
+        <v>95873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>2362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346139</v>
+        <v>346165</v>
       </c>
       <c r="R2" t="n">
-        <v>6611366</v>
+        <v>6611336</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129435802</v>
+        <v>129315527</v>
       </c>
       <c r="B3" t="n">
-        <v>95870</v>
+        <v>97287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2362</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346165</v>
+        <v>346139</v>
       </c>
       <c r="R3" t="n">
-        <v>6611336</v>
+        <v>6611366</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129314039</v>
       </c>
       <c r="B4" t="n">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,43 +982,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129315274</v>
+        <v>129436156</v>
       </c>
       <c r="B5" t="n">
-        <v>4871</v>
+        <v>97287</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101675</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346052</v>
+        <v>346164</v>
       </c>
       <c r="R5" t="n">
-        <v>6611326</v>
+        <v>6611359</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,38 +1084,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129436156</v>
+        <v>129315274</v>
       </c>
       <c r="B6" t="n">
-        <v>97284</v>
+        <v>4872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>101675</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346164</v>
+        <v>346052</v>
       </c>
       <c r="R6" t="n">
-        <v>6611359</v>
+        <v>6611326</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129314197</v>
+        <v>129314075</v>
       </c>
       <c r="B7" t="n">
-        <v>91801</v>
+        <v>95873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1202,26 +1202,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1229,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346210</v>
+        <v>346120</v>
       </c>
       <c r="R7" t="n">
-        <v>6611444</v>
+        <v>6611435</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1292,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129314075</v>
+        <v>129314197</v>
       </c>
       <c r="B8" t="n">
-        <v>95870</v>
+        <v>91804</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,27 +1304,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2362</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346120</v>
+        <v>346210</v>
       </c>
       <c r="R8" t="n">
-        <v>6611435</v>
+        <v>6611444</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1397,7 +1397,7 @@
         <v>129314960</v>
       </c>
       <c r="B9" t="n">
-        <v>97284</v>
+        <v>97287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>129314846</v>
       </c>
       <c r="B10" t="n">
-        <v>96276</v>
+        <v>96279</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>129435846</v>
       </c>
       <c r="B11" t="n">
-        <v>97711</v>
+        <v>97714</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129314731</v>
       </c>
       <c r="B12" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>129314127</v>
       </c>
       <c r="B13" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129435692</v>
       </c>
       <c r="B14" t="n">
-        <v>80331</v>
+        <v>80334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>129315075</v>
       </c>
       <c r="B15" t="n">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>129314057</v>
       </c>
       <c r="B16" t="n">
-        <v>97284</v>
+        <v>97287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>129314097</v>
       </c>
       <c r="B17" t="n">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>129435982</v>
       </c>
       <c r="B18" t="n">
-        <v>97284</v>
+        <v>97287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>129314070</v>
       </c>
       <c r="B19" t="n">
-        <v>97722</v>
+        <v>97725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129433339</v>
       </c>
       <c r="B20" t="n">
-        <v>96264</v>
+        <v>96267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>129433280</v>
       </c>
       <c r="B21" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>129433259</v>
       </c>
       <c r="B22" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,42 +2822,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314535</v>
+        <v>129314180</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>97662</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2865,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346219</v>
+        <v>346106</v>
       </c>
       <c r="R23" t="n">
-        <v>6611489</v>
+        <v>6611460</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2903,17 +2899,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2932,38 +2924,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129314180</v>
+        <v>129314535</v>
       </c>
       <c r="B24" t="n">
-        <v>97659</v>
+        <v>57907</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2569</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2971,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346106</v>
+        <v>346219</v>
       </c>
       <c r="R24" t="n">
-        <v>6611460</v>
+        <v>6611489</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3009,13 +3005,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>129435818</v>
       </c>
       <c r="B25" t="n">
-        <v>96264</v>
+        <v>96267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129314244</v>
       </c>
       <c r="B26" t="n">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>129435288</v>
       </c>
       <c r="B27" t="n">
-        <v>75372</v>
+        <v>75375</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129435802</v>
+        <v>129315527</v>
       </c>
       <c r="B2" t="n">
-        <v>95873</v>
+        <v>97292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2362</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346165</v>
+        <v>346139</v>
       </c>
       <c r="R2" t="n">
-        <v>6611336</v>
+        <v>6611366</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129315527</v>
+        <v>129435802</v>
       </c>
       <c r="B3" t="n">
-        <v>97287</v>
+        <v>95878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>2362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346139</v>
+        <v>346165</v>
       </c>
       <c r="R3" t="n">
-        <v>6611366</v>
+        <v>6611336</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129314039</v>
+        <v>129315274</v>
       </c>
       <c r="B4" t="n">
-        <v>5199</v>
+        <v>4872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,28 +890,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>101675</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346083</v>
+        <v>346052</v>
       </c>
       <c r="R4" t="n">
-        <v>6611330</v>
+        <v>6611326</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -982,38 +986,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129436156</v>
+        <v>129314039</v>
       </c>
       <c r="B5" t="n">
-        <v>97287</v>
+        <v>5199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1021,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346164</v>
+        <v>346083</v>
       </c>
       <c r="R5" t="n">
-        <v>6611359</v>
+        <v>6611330</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,43 +1089,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129315274</v>
+        <v>129436156</v>
       </c>
       <c r="B6" t="n">
-        <v>4872</v>
+        <v>97292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101675</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346052</v>
+        <v>346164</v>
       </c>
       <c r="R6" t="n">
-        <v>6611326</v>
+        <v>6611359</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>129314075</v>
       </c>
       <c r="B7" t="n">
-        <v>95873</v>
+        <v>95878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>129314197</v>
       </c>
       <c r="B8" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129314960</v>
       </c>
       <c r="B9" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>129314846</v>
       </c>
       <c r="B10" t="n">
-        <v>96279</v>
+        <v>96284</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129435846</v>
+        <v>129314731</v>
       </c>
       <c r="B11" t="n">
-        <v>97714</v>
+        <v>101257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         <v>346116</v>
       </c>
       <c r="R11" t="n">
-        <v>6611445</v>
+        <v>6611431</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129314731</v>
+        <v>129435846</v>
       </c>
       <c r="B12" t="n">
-        <v>101252</v>
+        <v>97719</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         <v>346116</v>
       </c>
       <c r="R12" t="n">
-        <v>6611431</v>
+        <v>6611445</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129435692</v>
       </c>
       <c r="B14" t="n">
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,38 +2109,39 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314057</v>
+        <v>129314097</v>
       </c>
       <c r="B16" t="n">
-        <v>97287</v>
+        <v>5199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2148,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346105</v>
+        <v>346210</v>
       </c>
       <c r="R16" t="n">
-        <v>6611430</v>
+        <v>6611507</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2211,39 +2212,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129314097</v>
+        <v>129435982</v>
       </c>
       <c r="B17" t="n">
-        <v>5199</v>
+        <v>97292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>346210</v>
+        <v>346198</v>
       </c>
       <c r="R17" t="n">
-        <v>6611507</v>
+        <v>6611512</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129435982</v>
+        <v>129314057</v>
       </c>
       <c r="B18" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>346198</v>
+        <v>346105</v>
       </c>
       <c r="R18" t="n">
-        <v>6611512</v>
+        <v>6611430</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>129314070</v>
       </c>
       <c r="B19" t="n">
-        <v>97725</v>
+        <v>97730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,38 +2518,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433339</v>
+        <v>129433259</v>
       </c>
       <c r="B20" t="n">
-        <v>96267</v>
+        <v>79274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2557,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>346089</v>
+        <v>346217</v>
       </c>
       <c r="R20" t="n">
-        <v>6611400</v>
+        <v>6611376</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2623,7 +2622,7 @@
         <v>129433280</v>
       </c>
       <c r="B21" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2721,37 +2720,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433259</v>
+        <v>129433339</v>
       </c>
       <c r="B22" t="n">
-        <v>79269</v>
+        <v>96272</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>346217</v>
+        <v>346089</v>
       </c>
       <c r="R22" t="n">
-        <v>6611376</v>
+        <v>6611400</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2825,7 +2825,7 @@
         <v>129314180</v>
       </c>
       <c r="B23" t="n">
-        <v>97662</v>
+        <v>97667</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,42 +2924,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129314535</v>
+        <v>129435818</v>
       </c>
       <c r="B24" t="n">
-        <v>57907</v>
+        <v>96272</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2967,13 +2963,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346219</v>
+        <v>346107</v>
       </c>
       <c r="R24" t="n">
-        <v>6611489</v>
+        <v>6611387</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3005,17 +3001,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3034,38 +3026,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129435818</v>
+        <v>129314535</v>
       </c>
       <c r="B25" t="n">
-        <v>96267</v>
+        <v>57912</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3073,13 +3069,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>346107</v>
+        <v>346219</v>
       </c>
       <c r="R25" t="n">
-        <v>6611387</v>
+        <v>6611489</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3111,13 +3107,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>129435288</v>
       </c>
       <c r="B27" t="n">
-        <v>75375</v>
+        <v>75380</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -2109,39 +2109,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314097</v>
+        <v>129314057</v>
       </c>
       <c r="B16" t="n">
-        <v>5199</v>
+        <v>97292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2149,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346210</v>
+        <v>346105</v>
       </c>
       <c r="R16" t="n">
-        <v>6611507</v>
+        <v>6611430</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2212,38 +2211,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129435982</v>
+        <v>129314097</v>
       </c>
       <c r="B17" t="n">
-        <v>97292</v>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>346198</v>
+        <v>346210</v>
       </c>
       <c r="R17" t="n">
-        <v>6611512</v>
+        <v>6611507</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129314057</v>
+        <v>129435982</v>
       </c>
       <c r="B18" t="n">
         <v>97292</v>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>346105</v>
+        <v>346198</v>
       </c>
       <c r="R18" t="n">
-        <v>6611430</v>
+        <v>6611512</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433259</v>
+        <v>129433280</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>91809</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>346217</v>
+        <v>346163</v>
       </c>
       <c r="R20" t="n">
-        <v>6611376</v>
+        <v>6611351</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2619,32 +2619,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433280</v>
+        <v>129433259</v>
       </c>
       <c r="B21" t="n">
-        <v>91809</v>
+        <v>79274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>346163</v>
+        <v>346217</v>
       </c>
       <c r="R21" t="n">
-        <v>6611351</v>
+        <v>6611376</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129315527</v>
+        <v>129314057</v>
       </c>
       <c r="B2" t="n">
-        <v>97292</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346139</v>
+        <v>346105</v>
       </c>
       <c r="R2" t="n">
-        <v>6611366</v>
+        <v>6611430</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129435802</v>
+        <v>129314960</v>
       </c>
       <c r="B3" t="n">
-        <v>95878</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2362</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346165</v>
+        <v>346089</v>
       </c>
       <c r="R3" t="n">
-        <v>6611336</v>
+        <v>6611325</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,43 +879,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129315274</v>
+        <v>129315527</v>
       </c>
       <c r="B4" t="n">
-        <v>4872</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101675</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346052</v>
+        <v>346139</v>
       </c>
       <c r="R4" t="n">
-        <v>6611326</v>
+        <v>6611366</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,39 +981,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129314039</v>
+        <v>129435982</v>
       </c>
       <c r="B5" t="n">
-        <v>5199</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,13 +1020,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346083</v>
+        <v>346198</v>
       </c>
       <c r="R5" t="n">
-        <v>6611330</v>
+        <v>6611512</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1086,7 @@
         <v>129436156</v>
       </c>
       <c r="B6" t="n">
-        <v>97292</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1188,7 @@
         <v>129314075</v>
       </c>
       <c r="B7" t="n">
-        <v>95878</v>
+        <v>95944</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129314197</v>
+        <v>129435802</v>
       </c>
       <c r="B8" t="n">
-        <v>91809</v>
+        <v>95944</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1304,26 +1298,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>2362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1331,13 +1326,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346210</v>
+        <v>346165</v>
       </c>
       <c r="R8" t="n">
-        <v>6611444</v>
+        <v>6611336</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,32 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129314960</v>
+        <v>129314180</v>
       </c>
       <c r="B9" t="n">
-        <v>97292</v>
+        <v>97733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>346089</v>
+        <v>346106</v>
       </c>
       <c r="R9" t="n">
-        <v>6611325</v>
+        <v>6611460</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129314846</v>
+        <v>129435846</v>
       </c>
       <c r="B10" t="n">
-        <v>96284</v>
+        <v>97785</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1502,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2813</v>
+        <v>2606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,13 +1530,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346170</v>
+        <v>346116</v>
       </c>
       <c r="R10" t="n">
-        <v>6611332</v>
+        <v>6611445</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129314731</v>
+        <v>129314070</v>
       </c>
       <c r="B11" t="n">
-        <v>101257</v>
+        <v>97796</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2609</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>346116</v>
+        <v>346120</v>
       </c>
       <c r="R11" t="n">
-        <v>6611431</v>
+        <v>6611435</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129435846</v>
+        <v>129433339</v>
       </c>
       <c r="B12" t="n">
-        <v>97719</v>
+        <v>96338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1734,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>346116</v>
+        <v>346089</v>
       </c>
       <c r="R12" t="n">
-        <v>6611445</v>
+        <v>6611400</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129314127</v>
+        <v>129435818</v>
       </c>
       <c r="B13" t="n">
-        <v>4775</v>
+        <v>96338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,28 +1808,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1842,13 +1836,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>346104</v>
+        <v>346107</v>
       </c>
       <c r="R13" t="n">
-        <v>6611325</v>
+        <v>6611387</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1905,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129435692</v>
+        <v>129314846</v>
       </c>
       <c r="B14" t="n">
-        <v>80339</v>
+        <v>96350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,26 +1910,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1943,13 +1938,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>346110</v>
+        <v>346170</v>
       </c>
       <c r="R14" t="n">
-        <v>6611458</v>
+        <v>6611332</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129315075</v>
+        <v>129314197</v>
       </c>
       <c r="B15" t="n">
-        <v>5199</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,28 +2012,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2046,10 +2039,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>346114</v>
+        <v>346210</v>
       </c>
       <c r="R15" t="n">
-        <v>6611402</v>
+        <v>6611444</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2109,38 +2102,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129314057</v>
+        <v>129433280</v>
       </c>
       <c r="B16" t="n">
-        <v>97292</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2148,13 +2140,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>346105</v>
+        <v>346163</v>
       </c>
       <c r="R16" t="n">
-        <v>6611430</v>
+        <v>6611351</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2211,39 +2203,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129314097</v>
+        <v>129433259</v>
       </c>
       <c r="B17" t="n">
-        <v>5199</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2251,13 +2241,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>346210</v>
+        <v>346217</v>
       </c>
       <c r="R17" t="n">
-        <v>6611507</v>
+        <v>6611376</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2314,10 +2304,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129435982</v>
+        <v>129435288</v>
       </c>
       <c r="B18" t="n">
-        <v>97292</v>
+        <v>75428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2325,27 +2315,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>346198</v>
+        <v>346193</v>
       </c>
       <c r="R18" t="n">
-        <v>6611512</v>
+        <v>6611282</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2416,38 +2405,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129314070</v>
+        <v>129314535</v>
       </c>
       <c r="B19" t="n">
-        <v>97730</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2609</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2455,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>346120</v>
+        <v>346219</v>
       </c>
       <c r="R19" t="n">
-        <v>6611435</v>
+        <v>6611489</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2493,13 +2486,17 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2518,10 +2515,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129433280</v>
+        <v>129314127</v>
       </c>
       <c r="B20" t="n">
-        <v>91809</v>
+        <v>4775</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,26 +2526,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2556,13 +2555,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>346163</v>
+        <v>346104</v>
       </c>
       <c r="R20" t="n">
-        <v>6611351</v>
+        <v>6611325</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2619,37 +2618,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129433259</v>
+        <v>129315274</v>
       </c>
       <c r="B21" t="n">
-        <v>79274</v>
+        <v>4872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>101675</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2657,13 +2662,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>346217</v>
+        <v>346052</v>
       </c>
       <c r="R21" t="n">
-        <v>6611376</v>
+        <v>6611326</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129433339</v>
+        <v>129314039</v>
       </c>
       <c r="B22" t="n">
-        <v>96272</v>
+        <v>5199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,27 +2736,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2759,13 +2765,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>346089</v>
+        <v>346083</v>
       </c>
       <c r="R22" t="n">
-        <v>6611400</v>
+        <v>6611330</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129314180</v>
+        <v>129314097</v>
       </c>
       <c r="B23" t="n">
-        <v>97667</v>
+        <v>5199</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,27 +2839,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2861,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>346106</v>
+        <v>346210</v>
       </c>
       <c r="R23" t="n">
-        <v>6611460</v>
+        <v>6611507</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2924,10 +2931,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129435818</v>
+        <v>129314244</v>
       </c>
       <c r="B24" t="n">
-        <v>96272</v>
+        <v>5199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2935,27 +2942,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2963,13 +2971,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>346107</v>
+        <v>346131</v>
       </c>
       <c r="R24" t="n">
-        <v>6611387</v>
+        <v>6611377</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3026,27 +3034,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129314535</v>
+        <v>129315075</v>
       </c>
       <c r="B25" t="n">
-        <v>57912</v>
+        <v>5199</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3055,13 +3063,10 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3069,10 +3074,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>346219</v>
+        <v>346114</v>
       </c>
       <c r="R25" t="n">
-        <v>6611489</v>
+        <v>6611402</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3107,17 +3112,13 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3136,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129314244</v>
+        <v>129314731</v>
       </c>
       <c r="B26" t="n">
-        <v>5199</v>
+        <v>101325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,28 +3148,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>346131</v>
+        <v>346116</v>
       </c>
       <c r="R26" t="n">
-        <v>6611377</v>
+        <v>6611431</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129435288</v>
+        <v>129435692</v>
       </c>
       <c r="B27" t="n">
-        <v>75380</v>
+        <v>80392</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>346193</v>
+        <v>346110</v>
       </c>
       <c r="R27" t="n">
-        <v>6611282</v>
+        <v>6611458</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 42165-2023 artfynd.xlsx
+++ b/artfynd/A 42165-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314057</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314960</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129315527</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129435982</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129436156</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314075</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129435802</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314180</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129435846</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314070</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129433339</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129435818</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314846</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2099,6 +2169,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314197</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2200,6 +2275,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129433280</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2301,6 +2381,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129433259</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2402,6 +2487,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129435288</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2512,6 +2602,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314535</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2615,6 +2710,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314127</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2722,6 +2822,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129315274</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2825,6 +2930,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314039</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2928,6 +3038,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314097</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3031,6 +3146,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314244</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3134,6 +3254,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129315075</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3236,6 +3361,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129314731</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3337,8 +3467,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129435692</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>